--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2150,6 +2150,318 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128761555</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86956</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N Björklunda, N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516459</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6574429</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128761347</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86828</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Björklunda, N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516462</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6574406</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128762134</v>
+      </c>
+      <c r="B17" t="n">
+        <v>86828</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N Björklunda, N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516450</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6574471</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86828</v>
+        <v>86855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86828</v>
+        <v>86855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86855</v>
+        <v>86859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86855</v>
+        <v>86859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86859</v>
+        <v>86860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86859</v>
+        <v>86860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>87014</v>
+        <v>87021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -2155,7 +2155,7 @@
         <v>128761555</v>
       </c>
       <c r="B15" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128761347</v>
       </c>
       <c r="B16" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128762134</v>
       </c>
       <c r="B17" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30728-2021 artfynd.xlsx
+++ b/artfynd/A 30728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55917860</v>
+        <v>96099940</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Munkatorp, Nrk</t>
+          <t>E18, Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516412.1990494126</v>
+        <v>516401</v>
       </c>
       <c r="R2" t="n">
-        <v>6574419.851338636</v>
+        <v>6574383</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96099940</v>
+        <v>103870567</v>
       </c>
       <c r="B3" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>E18, Örebro, Nrk</t>
+          <t>N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516401.1076642352</v>
+        <v>516431</v>
       </c>
       <c r="R3" t="n">
-        <v>6574382.530014429</v>
+        <v>6574529</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -858,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96101582</v>
+        <v>103872172</v>
       </c>
       <c r="B4" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,35 +882,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Björklunda , Nrk</t>
+          <t>N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516421.45742118</v>
+        <v>516469</v>
       </c>
       <c r="R4" t="n">
-        <v>6574526.092942568</v>
+        <v>6574493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,22 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,51 +969,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96099629</v>
+        <v>103872256</v>
       </c>
       <c r="B5" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örebro, Nrk</t>
+          <t>N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516399.6609084563</v>
+        <v>516478</v>
       </c>
       <c r="R5" t="n">
-        <v>6574480.557011386</v>
+        <v>6574491</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96090636</v>
+        <v>111309284</v>
       </c>
       <c r="B6" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,21 +1105,24 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Björklunda, Nrk</t>
+          <t>N Björklunda, N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516471.5726595792</v>
+        <v>516410</v>
       </c>
       <c r="R6" t="n">
-        <v>6574410.40741619</v>
+        <v>6574463</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,22 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1160,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,41 +1178,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96090603</v>
+        <v>96090636</v>
       </c>
       <c r="B7" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3286</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516443.2288221862</v>
+        <v>516472</v>
       </c>
       <c r="R7" t="n">
-        <v>6574459.301046672</v>
+        <v>6574410</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,19 +1257,9 @@
           <t>2021-09-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,53 +1287,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96090643</v>
+        <v>96099629</v>
       </c>
       <c r="B8" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Björklunda, Nrk</t>
+          <t>Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516474.5062829911</v>
+        <v>516400</v>
       </c>
       <c r="R8" t="n">
-        <v>6574441.566187239</v>
+        <v>6574481</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1439,22 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1367,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1482,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103870574</v>
+        <v>103872504</v>
       </c>
       <c r="B9" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,35 +1396,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Björklunda, Nrk</t>
+          <t>N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516429.1205370935</v>
+        <v>516433</v>
       </c>
       <c r="R9" t="n">
-        <v>6574528.168430888</v>
+        <v>6574508</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1556,19 +1454,9 @@
           <t>2022-10-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103872504</v>
+        <v>112742133</v>
       </c>
       <c r="B10" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,17 +1515,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Björklunda , Nrk</t>
+          <t>N Björklunda , N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516432.2755723943</v>
+        <v>516485</v>
       </c>
       <c r="R10" t="n">
-        <v>6574508.269543659</v>
+        <v>6574480</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,22 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,67 +1581,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111309284</v>
+        <v>111704069</v>
       </c>
       <c r="B11" t="n">
-        <v>89601</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>3279</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Maskfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Clavaria fragilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Holmsk., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Björklunda (N Björklunda), Nrk</t>
+          <t>N Björklunda , N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516409.9676129111</v>
+        <v>516436</v>
       </c>
       <c r="R11" t="n">
-        <v>6574462.731124463</v>
+        <v>6574480</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,22 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,6 +1663,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1834,37 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111704069</v>
+        <v>96090603</v>
       </c>
       <c r="B12" t="n">
-        <v>84997</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3279</v>
+        <v>3286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maskfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Clavaria fragilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Holmsk.:Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,17 +1716,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Björklunda  (N Björklunda ), Nrk</t>
+          <t>N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516437</v>
+        <v>516443</v>
       </c>
       <c r="R12" t="n">
-        <v>6574480</v>
+        <v>6574459</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1907,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,56 +1783,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111703377</v>
+        <v>96101582</v>
       </c>
       <c r="B13" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>3286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N Björklunda (N Björklunda), Nrk</t>
+          <t>N Björklunda , Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516440</v>
+        <v>516421</v>
       </c>
       <c r="R13" t="n">
-        <v>6574461</v>
+        <v>6574526</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,12 +1849,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,7 +1863,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2046,53 +1881,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111703549</v>
+        <v>128761347</v>
       </c>
       <c r="B14" t="n">
-        <v>88934</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5741</v>
+        <v>3611</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Björklunda (N Björklunda), Nrk</t>
+          <t>N Björklunda, N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516400</v>
+        <v>516462</v>
       </c>
       <c r="R14" t="n">
-        <v>6574444</v>
+        <v>6574406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,12 +1955,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +1969,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2152,10 +1987,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128761555</v>
+        <v>128762134</v>
       </c>
       <c r="B15" t="n">
-        <v>87023</v>
+        <v>87247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,34 +1998,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>N Björklunda, N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516459</v>
+        <v>516450</v>
       </c>
       <c r="R15" t="n">
-        <v>6574429</v>
+        <v>6574471</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2231,6 +2077,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2249,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128761347</v>
+        <v>128761555</v>
       </c>
       <c r="B16" t="n">
-        <v>86895</v>
+        <v>87375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,46 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>N Björklunda, N Björklunda, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516462</v>
+        <v>516459</v>
       </c>
       <c r="R16" t="n">
-        <v>6574406</v>
+        <v>6574429</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128762134</v>
+        <v>111703377</v>
       </c>
       <c r="B17" t="n">
-        <v>86895</v>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,33 +2204,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3611</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2401,13 +2231,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516450</v>
+        <v>516440</v>
       </c>
       <c r="R17" t="n">
-        <v>6574471</v>
+        <v>6574461</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,12 +2261,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,6 +2291,403 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103870574</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516429</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6574528</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96090643</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516474</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6574441</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111703549</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N Björklunda, N Björklunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516400</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6574444</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>55917860</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Munkatorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516412</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6574420</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2015-10-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2015-10-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
